--- a/Sales_Inventory.xlsx
+++ b/Sales_Inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -590,7 +590,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
@@ -3255,40 +3255,368 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Direct Sale</t>
+          <t>Sale</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>DE26002N</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>343.8</v>
+      </c>
+      <c r="F68" s="4">
+        <f>D68*E68</f>
+        <v/>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H68" s="4">
+        <f>F68-G68</f>
+        <v/>
+      </c>
+      <c r="I68" s="5">
+        <f>IF(F68&gt;0, H68/F68, 0)</f>
+        <v/>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>DE26050B</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>336.84</v>
+      </c>
+      <c r="F69" s="4">
+        <f>D69*E69</f>
+        <v/>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H69" s="4">
+        <f>F69-G69</f>
+        <v/>
+      </c>
+      <c r="I69" s="5">
+        <f>IF(F69&gt;0, H69/F69, 0)</f>
+        <v/>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>DE26002R</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>366.3</v>
+      </c>
+      <c r="F70" s="4">
+        <f>D70*E70</f>
+        <v/>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H70" s="4">
+        <f>F70-G70</f>
+        <v/>
+      </c>
+      <c r="I70" s="5">
+        <f>IF(F70&gt;0, H70/F70, 0)</f>
+        <v/>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>DE26002R</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>333.76</v>
+      </c>
+      <c r="F71" s="4">
+        <f>D71*E71</f>
+        <v/>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H71" s="4">
+        <f>F71-G71</f>
+        <v/>
+      </c>
+      <c r="I71" s="5">
+        <f>IF(F71&gt;0, H71/F71, 0)</f>
+        <v/>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>DE26009G</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>306.01</v>
+      </c>
+      <c r="F72" s="4">
+        <f>D72*E72</f>
+        <v/>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="H72" s="4">
+        <f>F72-G72</f>
+        <v/>
+      </c>
+      <c r="I72" s="5">
+        <f>IF(F72&gt;0, H72/F72, 0)</f>
+        <v/>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>DE26050B</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>338.08</v>
+      </c>
+      <c r="F73" s="4">
+        <f>D73*E73</f>
+        <v/>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H73" s="4">
+        <f>F73-G73</f>
+        <v/>
+      </c>
+      <c r="I73" s="5">
+        <f>IF(F73&gt;0, H73/F73, 0)</f>
+        <v/>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>DE26077R</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>317.57</v>
+      </c>
+      <c r="F74" s="4">
+        <f>D74*E74</f>
+        <v/>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="H74" s="4">
+        <f>F74-G74</f>
+        <v/>
+      </c>
+      <c r="I74" s="5">
+        <f>IF(F74&gt;0, H74/F74, 0)</f>
+        <v/>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>DE26081M</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>315.67</v>
+      </c>
+      <c r="F75" s="4">
+        <f>D75*E75</f>
+        <v/>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H75" s="4">
+        <f>F75-G75</f>
+        <v/>
+      </c>
+      <c r="I75" s="5">
+        <f>IF(F75&gt;0, H75/F75, 0)</f>
+        <v/>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr"/>
-      <c r="C68" s="6" t="inlineStr"/>
-      <c r="D68" s="7">
-        <f>SUM(D2:D67)</f>
-        <v/>
-      </c>
-      <c r="E68" s="6" t="inlineStr"/>
-      <c r="F68" s="8">
-        <f>SUM(F2:F67)</f>
-        <v/>
-      </c>
-      <c r="G68" s="8">
-        <f>SUM(G2:G67)</f>
-        <v/>
-      </c>
-      <c r="H68" s="8">
-        <f>SUM(H2:H67)</f>
-        <v/>
-      </c>
-      <c r="I68" s="9">
-        <f>IF(F68&gt;0, H68/F68, 0)</f>
-        <v/>
-      </c>
-      <c r="J68" s="6" t="inlineStr"/>
+      <c r="B76" s="6" t="inlineStr"/>
+      <c r="C76" s="6" t="inlineStr"/>
+      <c r="D76" s="7">
+        <f>SUM(D2:D75)</f>
+        <v/>
+      </c>
+      <c r="E76" s="6" t="inlineStr"/>
+      <c r="F76" s="8">
+        <f>SUM(F2:F75)</f>
+        <v/>
+      </c>
+      <c r="G76" s="8">
+        <f>SUM(G2:G75)</f>
+        <v/>
+      </c>
+      <c r="H76" s="8">
+        <f>SUM(H2:H75)</f>
+        <v/>
+      </c>
+      <c r="I76" s="9">
+        <f>IF(F76&gt;0, H76/F76, 0)</f>
+        <v/>
+      </c>
+      <c r="J76" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3584,7 +3912,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -3607,7 +3935,7 @@
         <v/>
       </c>
       <c r="J7" s="4" t="n">
-        <v>102.09</v>
+        <v>210.89</v>
       </c>
       <c r="K7" s="2">
         <f>IF(G7&gt;10, "In Stock", IF(G7&gt;0, "Low Stock", IF(G7=0, "Out of Stock", "Over Sold")))</f>
@@ -3624,7 +3952,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -3647,7 +3975,7 @@
         <v/>
       </c>
       <c r="J8" s="4" t="n">
-        <v>314.13</v>
+        <v>544.1900000000001</v>
       </c>
       <c r="K8" s="2">
         <f>IF(G8&gt;10, "In Stock", IF(G8&gt;0, "Low Stock", IF(G8=0, "Out of Stock", "Over Sold")))</f>
@@ -4344,7 +4672,7 @@
         <v>12</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>0</v>
@@ -4367,7 +4695,7 @@
         <v/>
       </c>
       <c r="J26" s="4" t="n">
-        <v>284.14</v>
+        <v>365.15</v>
       </c>
       <c r="K26" s="2">
         <f>IF(G26&gt;10, "In Stock", IF(G26&gt;0, "Low Stock", IF(G26=0, "Out of Stock", "Over Sold")))</f>
@@ -4664,7 +4992,7 @@
         <v>10</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -4687,7 +5015,7 @@
         <v/>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0</v>
+        <v>204.92</v>
       </c>
       <c r="K34" s="2">
         <f>IF(G34&gt;10, "In Stock", IF(G34&gt;0, "Low Stock", IF(G34=0, "Out of Stock", "Over Sold")))</f>
@@ -4824,7 +5152,7 @@
         <v>12</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0</v>
@@ -4847,7 +5175,7 @@
         <v/>
       </c>
       <c r="J38" s="4" t="n">
-        <v>488.18</v>
+        <v>585.75</v>
       </c>
       <c r="K38" s="2">
         <f>IF(G38&gt;10, "In Stock", IF(G38&gt;0, "Low Stock", IF(G38=0, "Out of Stock", "Over Sold")))</f>
@@ -4867,10 +5195,10 @@
         <v>6</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>0</v>
@@ -4904,7 +5232,7 @@
         <v>10</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0</v>
@@ -4927,7 +5255,7 @@
         <v/>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0</v>
+        <v>80.67</v>
       </c>
       <c r="K40" s="2">
         <f>IF(G40&gt;10, "In Stock", IF(G40&gt;0, "Low Stock", IF(G40=0, "Out of Stock", "Over Sold")))</f>
@@ -5548,10 +5876,14 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>In Transit</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -5652,7 +5984,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="37" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
@@ -5975,10 +6307,14 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>In Transit</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -6257,7 +6593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6737,17 +7073,49 @@
       <c r="D29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>332.49</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>316.36</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr"/>
-      <c r="C30" s="8">
-        <f>SUM(C2:C29)</f>
-        <v/>
-      </c>
-      <c r="D30" s="6" t="inlineStr"/>
+      <c r="B32" s="6" t="inlineStr"/>
+      <c r="C32" s="8">
+        <f>SUM(C2:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6760,12 +7128,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
@@ -7029,18 +7397,39 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Credited (+)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>269.85</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>-112541.37</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="8">
-        <f>SUM(D2:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="8">
+        <f>SUM(D2:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7053,7 +7442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7724,33 +8113,87 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>1046.94</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>705</v>
+      </c>
+      <c r="F25" s="4">
+        <f>D25-E25</f>
+        <v/>
+      </c>
+      <c r="G25" s="5">
+        <f>IF(D25&gt;0, F25/D25, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>1611.09</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F26" s="4">
+        <f>D26-E26</f>
+        <v/>
+      </c>
+      <c r="G26" s="5">
+        <f>IF(D26&gt;0, F26/D26, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>SUM(B2:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="7">
-        <f>SUM(C2:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="8">
-        <f>SUM(D2:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="8">
-        <f>SUM(E2:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="8">
-        <f>SUM(F2:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="9">
-        <f>IF(D25&gt;0, F25/D25, 0)</f>
+      <c r="B27" s="7">
+        <f>SUM(B2:B26)</f>
+        <v/>
+      </c>
+      <c r="C27" s="7">
+        <f>SUM(C2:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="8">
+        <f>SUM(D2:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="8">
+        <f>SUM(E2:E26)</f>
+        <v/>
+      </c>
+      <c r="F27" s="8">
+        <f>SUM(F2:F26)</f>
+        <v/>
+      </c>
+      <c r="G27" s="9">
+        <f>IF(D27&gt;0, F27/D27, 0)</f>
         <v/>
       </c>
     </row>
@@ -7765,7 +8208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -8193,18 +8636,54 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>332.49</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>316.36</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>SUM(B2:B23)</f>
-        <v/>
-      </c>
-      <c r="C24" s="6" t="inlineStr"/>
-      <c r="D24" s="8">
-        <f>SUM(D2:D23)</f>
+      <c r="B26" s="7">
+        <f>SUM(B2:B25)</f>
+        <v/>
+      </c>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="8">
+        <f>SUM(D2:D25)</f>
         <v/>
       </c>
     </row>

--- a/Sales_Inventory.xlsx
+++ b/Sales_Inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3588,35 +3588,855 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>DE26002R</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>366.84</v>
+      </c>
+      <c r="F76" s="4">
+        <f>D76*E76</f>
+        <v/>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>470</v>
+      </c>
+      <c r="H76" s="4">
+        <f>F76-G76</f>
+        <v/>
+      </c>
+      <c r="I76" s="5">
+        <f>IF(F76&gt;0, H76/F76, 0)</f>
+        <v/>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>DE26003W</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>326</v>
+      </c>
+      <c r="F77" s="4">
+        <f>D77*E77</f>
+        <v/>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>438</v>
+      </c>
+      <c r="H77" s="4">
+        <f>F77-G77</f>
+        <v/>
+      </c>
+      <c r="I77" s="5">
+        <f>IF(F77&gt;0, H77/F77, 0)</f>
+        <v/>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>DE26006R</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>337.71</v>
+      </c>
+      <c r="F78" s="4">
+        <f>D78*E78</f>
+        <v/>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H78" s="4">
+        <f>F78-G78</f>
+        <v/>
+      </c>
+      <c r="I78" s="5">
+        <f>IF(F78&gt;0, H78/F78, 0)</f>
+        <v/>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>DE26009B</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>328.01</v>
+      </c>
+      <c r="F79" s="4">
+        <f>D79*E79</f>
+        <v/>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="H79" s="4">
+        <f>F79-G79</f>
+        <v/>
+      </c>
+      <c r="I79" s="5">
+        <f>IF(F79&gt;0, H79/F79, 0)</f>
+        <v/>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>DE26009Y</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>294.62</v>
+      </c>
+      <c r="F80" s="4">
+        <f>D80*E80</f>
+        <v/>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="H80" s="4">
+        <f>F80-G80</f>
+        <v/>
+      </c>
+      <c r="I80" s="5">
+        <f>IF(F80&gt;0, H80/F80, 0)</f>
+        <v/>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>DE26077R</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="F81" s="4">
+        <f>D81*E81</f>
+        <v/>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="H81" s="4">
+        <f>F81-G81</f>
+        <v/>
+      </c>
+      <c r="I81" s="5">
+        <f>IF(F81&gt;0, H81/F81, 0)</f>
+        <v/>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>DE26077Y</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>287.22</v>
+      </c>
+      <c r="F82" s="4">
+        <f>D82*E82</f>
+        <v/>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="H82" s="4">
+        <f>F82-G82</f>
+        <v/>
+      </c>
+      <c r="I82" s="5">
+        <f>IF(F82&gt;0, H82/F82, 0)</f>
+        <v/>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>DE26002N</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>365.53</v>
+      </c>
+      <c r="F83" s="4">
+        <f>D83*E83</f>
+        <v/>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H83" s="4">
+        <f>F83-G83</f>
+        <v/>
+      </c>
+      <c r="I83" s="5">
+        <f>IF(F83&gt;0, H83/F83, 0)</f>
+        <v/>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>DE26007N</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>302.73</v>
+      </c>
+      <c r="F84" s="4">
+        <f>D84*E84</f>
+        <v/>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H84" s="4">
+        <f>F84-G84</f>
+        <v/>
+      </c>
+      <c r="I84" s="5">
+        <f>IF(F84&gt;0, H84/F84, 0)</f>
+        <v/>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>DE26009G</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>295.66</v>
+      </c>
+      <c r="F85" s="4">
+        <f>D85*E85</f>
+        <v/>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="H85" s="4">
+        <f>F85-G85</f>
+        <v/>
+      </c>
+      <c r="I85" s="5">
+        <f>IF(F85&gt;0, H85/F85, 0)</f>
+        <v/>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>DE26077N</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>283.69</v>
+      </c>
+      <c r="F86" s="4">
+        <f>D86*E86</f>
+        <v/>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="H86" s="4">
+        <f>F86-G86</f>
+        <v/>
+      </c>
+      <c r="I86" s="5">
+        <f>IF(F86&gt;0, H86/F86, 0)</f>
+        <v/>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>DE26005N</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>304.28</v>
+      </c>
+      <c r="F87" s="4">
+        <f>D87*E87</f>
+        <v/>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H87" s="4">
+        <f>F87-G87</f>
+        <v/>
+      </c>
+      <c r="I87" s="5">
+        <f>IF(F87&gt;0, H87/F87, 0)</f>
+        <v/>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>DE26077R</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>318.53</v>
+      </c>
+      <c r="F88" s="4">
+        <f>D88*E88</f>
+        <v/>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="H88" s="4">
+        <f>F88-G88</f>
+        <v/>
+      </c>
+      <c r="I88" s="5">
+        <f>IF(F88&gt;0, H88/F88, 0)</f>
+        <v/>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>DE26016R</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>292.51</v>
+      </c>
+      <c r="F89" s="4">
+        <f>D89*E89</f>
+        <v/>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H89" s="4">
+        <f>F89-G89</f>
+        <v/>
+      </c>
+      <c r="I89" s="5">
+        <f>IF(F89&gt;0, H89/F89, 0)</f>
+        <v/>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>DE26077Y</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>297.2</v>
+      </c>
+      <c r="F90" s="4">
+        <f>D90*E90</f>
+        <v/>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="H90" s="4">
+        <f>F90-G90</f>
+        <v/>
+      </c>
+      <c r="I90" s="5">
+        <f>IF(F90&gt;0, H90/F90, 0)</f>
+        <v/>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>DE26077R</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>297.32</v>
+      </c>
+      <c r="F91" s="4">
+        <f>D91*E91</f>
+        <v/>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="H91" s="4">
+        <f>F91-G91</f>
+        <v/>
+      </c>
+      <c r="I91" s="5">
+        <f>IF(F91&gt;0, H91/F91, 0)</f>
+        <v/>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>DE26002R</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>366.43</v>
+      </c>
+      <c r="F92" s="4">
+        <f>D92*E92</f>
+        <v/>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H92" s="4">
+        <f>F92-G92</f>
+        <v/>
+      </c>
+      <c r="I92" s="5">
+        <f>IF(F92&gt;0, H92/F92, 0)</f>
+        <v/>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>DE26009B</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>305.08</v>
+      </c>
+      <c r="F93" s="4">
+        <f>D93*E93</f>
+        <v/>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="H93" s="4">
+        <f>F93-G93</f>
+        <v/>
+      </c>
+      <c r="I93" s="5">
+        <f>IF(F93&gt;0, H93/F93, 0)</f>
+        <v/>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>DE26030B</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>291.97</v>
+      </c>
+      <c r="F94" s="4">
+        <f>D94*E94</f>
+        <v/>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="H94" s="4">
+        <f>F94-G94</f>
+        <v/>
+      </c>
+      <c r="I94" s="5">
+        <f>IF(F94&gt;0, H94/F94, 0)</f>
+        <v/>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>DE26009G</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>305.27</v>
+      </c>
+      <c r="F95" s="4">
+        <f>D95*E95</f>
+        <v/>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="H95" s="4">
+        <f>F95-G95</f>
+        <v/>
+      </c>
+      <c r="I95" s="5">
+        <f>IF(F95&gt;0, H95/F95, 0)</f>
+        <v/>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr"/>
-      <c r="C76" s="6" t="inlineStr"/>
-      <c r="D76" s="7">
-        <f>SUM(D2:D75)</f>
-        <v/>
-      </c>
-      <c r="E76" s="6" t="inlineStr"/>
-      <c r="F76" s="8">
-        <f>SUM(F2:F75)</f>
-        <v/>
-      </c>
-      <c r="G76" s="8">
-        <f>SUM(G2:G75)</f>
-        <v/>
-      </c>
-      <c r="H76" s="8">
-        <f>SUM(H2:H75)</f>
-        <v/>
-      </c>
-      <c r="I76" s="9">
-        <f>IF(F76&gt;0, H76/F76, 0)</f>
-        <v/>
-      </c>
-      <c r="J76" s="6" t="inlineStr"/>
+      <c r="B96" s="6" t="inlineStr"/>
+      <c r="C96" s="6" t="inlineStr"/>
+      <c r="D96" s="7">
+        <f>SUM(D2:D95)</f>
+        <v/>
+      </c>
+      <c r="E96" s="6" t="inlineStr"/>
+      <c r="F96" s="8">
+        <f>SUM(F2:F95)</f>
+        <v/>
+      </c>
+      <c r="G96" s="8">
+        <f>SUM(G2:G95)</f>
+        <v/>
+      </c>
+      <c r="H96" s="8">
+        <f>SUM(H2:H95)</f>
+        <v/>
+      </c>
+      <c r="I96" s="9">
+        <f>IF(F96&gt;0, H96/F96, 0)</f>
+        <v/>
+      </c>
+      <c r="J96" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3912,7 +4732,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -3935,7 +4755,7 @@
         <v/>
       </c>
       <c r="J7" s="4" t="n">
-        <v>210.89</v>
+        <v>341.42</v>
       </c>
       <c r="K7" s="2">
         <f>IF(G7&gt;10, "In Stock", IF(G7&gt;0, "Low Stock", IF(G7=0, "Out of Stock", "Over Sold")))</f>
@@ -3952,13 +4772,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -3975,7 +4795,7 @@
         <v/>
       </c>
       <c r="J8" s="4" t="n">
-        <v>544.1900000000001</v>
+        <v>939.3000000000001</v>
       </c>
       <c r="K8" s="2">
         <f>IF(G8&gt;10, "In Stock", IF(G8&gt;0, "Low Stock", IF(G8=0, "Out of Stock", "Over Sold")))</f>
@@ -4032,7 +4852,7 @@
         <v>30</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -4055,7 +4875,7 @@
         <v/>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2185.64</v>
+        <v>2399.64</v>
       </c>
       <c r="K10" s="2">
         <f>IF(G10&gt;10, "In Stock", IF(G10&gt;0, "Low Stock", IF(G10=0, "Out of Stock", "Over Sold")))</f>
@@ -4232,7 +5052,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -4255,7 +5075,7 @@
         <v/>
       </c>
       <c r="J15" s="4" t="n">
-        <v>36.06</v>
+        <v>105.34</v>
       </c>
       <c r="K15" s="2">
         <f>IF(G15&gt;10, "In Stock", IF(G15&gt;0, "Low Stock", IF(G15=0, "Out of Stock", "Over Sold")))</f>
@@ -4352,7 +5172,7 @@
         <v>10</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>0</v>
@@ -4375,7 +5195,7 @@
         <v/>
       </c>
       <c r="J18" s="4" t="n">
-        <v>400.68</v>
+        <v>503.39</v>
       </c>
       <c r="K18" s="2">
         <f>IF(G18&gt;10, "In Stock", IF(G18&gt;0, "Low Stock", IF(G18=0, "Out of Stock", "Over Sold")))</f>
@@ -4432,7 +5252,7 @@
         <v>7</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
@@ -4455,7 +5275,7 @@
         <v/>
       </c>
       <c r="J20" s="4" t="n">
-        <v>181.53</v>
+        <v>249.26</v>
       </c>
       <c r="K20" s="2">
         <f>IF(G20&gt;10, "In Stock", IF(G20&gt;0, "Low Stock", IF(G20=0, "Out of Stock", "Over Sold")))</f>
@@ -4632,7 +5452,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>0</v>
@@ -4655,7 +5475,7 @@
         <v/>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0</v>
+        <v>183.09</v>
       </c>
       <c r="K25" s="2">
         <f>IF(G25&gt;10, "In Stock", IF(G25&gt;0, "Low Stock", IF(G25=0, "Out of Stock", "Over Sold")))</f>
@@ -4672,7 +5492,7 @@
         <v>12</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>0</v>
@@ -4695,7 +5515,7 @@
         <v/>
       </c>
       <c r="J26" s="4" t="n">
-        <v>365.15</v>
+        <v>516.08</v>
       </c>
       <c r="K26" s="2">
         <f>IF(G26&gt;10, "In Stock", IF(G26&gt;0, "Low Stock", IF(G26=0, "Out of Stock", "Over Sold")))</f>
@@ -4715,7 +5535,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>0</v>
@@ -4752,7 +5572,7 @@
         <v>13</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -4775,7 +5595,7 @@
         <v/>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0</v>
+        <v>69.62</v>
       </c>
       <c r="K28" s="2">
         <f>IF(G28&gt;10, "In Stock", IF(G28&gt;0, "Low Stock", IF(G28=0, "Out of Stock", "Over Sold")))</f>
@@ -4832,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>0</v>
@@ -4855,7 +5675,7 @@
         <v/>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0</v>
+        <v>57.51</v>
       </c>
       <c r="K30" s="2">
         <f>IF(G30&gt;10, "In Stock", IF(G30&gt;0, "Low Stock", IF(G30=0, "Out of Stock", "Over Sold")))</f>
@@ -4872,7 +5692,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
@@ -4895,7 +5715,7 @@
         <v/>
       </c>
       <c r="J31" s="4" t="n">
-        <v>262.55</v>
+        <v>349.52</v>
       </c>
       <c r="K31" s="2">
         <f>IF(G31&gt;10, "In Stock", IF(G31&gt;0, "Low Stock", IF(G31=0, "Out of Stock", "Over Sold")))</f>
@@ -5112,7 +5932,7 @@
         <v>6</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
@@ -5135,7 +5955,7 @@
         <v/>
       </c>
       <c r="J37" s="4" t="n">
-        <v>401.56</v>
+        <v>465.25</v>
       </c>
       <c r="K37" s="2">
         <f>IF(G37&gt;10, "In Stock", IF(G37&gt;0, "Low Stock", IF(G37=0, "Out of Stock", "Over Sold")))</f>
@@ -5152,7 +5972,7 @@
         <v>12</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0</v>
@@ -5175,7 +5995,7 @@
         <v/>
       </c>
       <c r="J38" s="4" t="n">
-        <v>585.75</v>
+        <v>905.17</v>
       </c>
       <c r="K38" s="2">
         <f>IF(G38&gt;10, "In Stock", IF(G38&gt;0, "Low Stock", IF(G38=0, "Out of Stock", "Over Sold")))</f>
@@ -5192,13 +6012,13 @@
         <v>12</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>0</v>
@@ -5215,7 +6035,7 @@
         <v/>
       </c>
       <c r="J39" s="4" t="n">
-        <v>463.42</v>
+        <v>607.84</v>
       </c>
       <c r="K39" s="2">
         <f>IF(G39&gt;10, "In Stock", IF(G39&gt;0, "Low Stock", IF(G39=0, "Out of Stock", "Over Sold")))</f>
@@ -5394,7 +6214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5833,10 +6653,14 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>In Transit</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -5936,31 +6760,121 @@
       <c r="L11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>RTO-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>DE26009P</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>302.1</v>
+      </c>
+      <c r="F12" s="4">
+        <f>D12*E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>In Transit</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Valmo AWB-VL0085381962558</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>RTO-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>DE26002R</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>315.37</v>
+      </c>
+      <c r="F13" s="4">
+        <f>D13*E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Delhivery AWB-1490841138769286</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr"/>
-      <c r="C12" s="6" t="inlineStr"/>
-      <c r="D12" s="7">
-        <f>SUM(D2:D11)</f>
-        <v/>
-      </c>
-      <c r="E12" s="6" t="inlineStr"/>
-      <c r="F12" s="8">
-        <f>SUM(F2:F11)</f>
-        <v/>
-      </c>
-      <c r="G12" s="8">
-        <f>SUM(G2:G11)</f>
-        <v/>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="6" t="inlineStr"/>
-      <c r="K12" s="6" t="inlineStr"/>
-      <c r="L12" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="7">
+        <f>SUM(D2:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="8">
+        <f>SUM(F2:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="8">
+        <f>SUM(G2:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5973,7 +6887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5984,7 +6898,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="37" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
@@ -6324,32 +7238,179 @@
       <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CR-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>DE26006R</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>309.82</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Product's quality or performance is not good</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>In Transit</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Valmo AWB-VLR082916892869</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CR-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>DE26002M</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>366.57</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Don't need the product anymore</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Found lower price elsewhere</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>In Transit</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Valmo AWB-VLR082918756063</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CR-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>DE26002N</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>343.8</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Wrong size delivered</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>In Transit</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Shadowfax AWB-R2567239146FPL</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="7">
-        <f>SUM(D2:D6)</f>
-        <v/>
-      </c>
-      <c r="E7" s="8">
-        <f>SUM(E2:E6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="8">
-        <f>SUM(F2:F6)</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
-      <c r="L7" s="6" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr"/>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="7">
+        <f>SUM(D2:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="8">
+        <f>SUM(E2:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="8">
+        <f>SUM(F2:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr"/>
+      <c r="M10" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7105,17 +8166,49 @@
       <c r="D31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>301.32</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr"/>
-      <c r="C32" s="8">
-        <f>SUM(C2:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="6" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr"/>
+      <c r="C34" s="8">
+        <f>SUM(C2:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7128,7 +8221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7418,18 +8511,102 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Credited (+)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>948.09</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>-111593.28</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Credited (+)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>310.13</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>-111283.15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Credited (+)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>593.05</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-110690.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Credited (+)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>1056.85</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>-109633.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="8">
-        <f>SUM(D2:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="6" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr"/>
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="8">
+        <f>SUM(D2:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7442,7 +8619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -8167,33 +9344,195 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>2051.4</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F27" s="4">
+        <f>D27-E27</f>
+        <v/>
+      </c>
+      <c r="G27" s="5">
+        <f>IF(D27&gt;0, F27/D27, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>868.09</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>665</v>
+      </c>
+      <c r="F28" s="4">
+        <f>D28-E28</f>
+        <v/>
+      </c>
+      <c r="G28" s="5">
+        <f>IF(D28&gt;0, F28/D28, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>1247.61</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>915</v>
+      </c>
+      <c r="F29" s="4">
+        <f>D29-E29</f>
+        <v/>
+      </c>
+      <c r="G29" s="5">
+        <f>IF(D29&gt;0, F29/D29, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>622.8099999999999</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>455</v>
+      </c>
+      <c r="F30" s="4">
+        <f>D30-E30</f>
+        <v/>
+      </c>
+      <c r="G30" s="5">
+        <f>IF(D30&gt;0, F30/D30, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>1184.35</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>895</v>
+      </c>
+      <c r="F31" s="4">
+        <f>D31-E31</f>
+        <v/>
+      </c>
+      <c r="G31" s="5">
+        <f>IF(D31&gt;0, F31/D31, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>1268.75</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>890</v>
+      </c>
+      <c r="F32" s="4">
+        <f>D32-E32</f>
+        <v/>
+      </c>
+      <c r="G32" s="5">
+        <f>IF(D32&gt;0, F32/D32, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B27" s="7">
-        <f>SUM(B2:B26)</f>
-        <v/>
-      </c>
-      <c r="C27" s="7">
-        <f>SUM(C2:C26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="8">
-        <f>SUM(D2:D26)</f>
-        <v/>
-      </c>
-      <c r="E27" s="8">
-        <f>SUM(E2:E26)</f>
-        <v/>
-      </c>
-      <c r="F27" s="8">
-        <f>SUM(F2:F26)</f>
-        <v/>
-      </c>
-      <c r="G27" s="9">
-        <f>IF(D27&gt;0, F27/D27, 0)</f>
+      <c r="B33" s="7">
+        <f>SUM(B2:B32)</f>
+        <v/>
+      </c>
+      <c r="C33" s="7">
+        <f>SUM(C2:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="8">
+        <f>SUM(D2:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="8">
+        <f>SUM(E2:E32)</f>
+        <v/>
+      </c>
+      <c r="F33" s="8">
+        <f>SUM(F2:F32)</f>
+        <v/>
+      </c>
+      <c r="G33" s="9">
+        <f>IF(D33&gt;0, F33/D33, 0)</f>
         <v/>
       </c>
     </row>
@@ -8208,7 +9547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -8672,18 +10011,54 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>301.32</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>SUM(B2:B25)</f>
-        <v/>
-      </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="8">
-        <f>SUM(D2:D25)</f>
+      <c r="B28" s="7">
+        <f>SUM(B2:B27)</f>
+        <v/>
+      </c>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="8">
+        <f>SUM(D2:D27)</f>
         <v/>
       </c>
     </row>

--- a/Sales_Inventory.xlsx
+++ b/Sales_Inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4408,35 +4408,76 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="inlineStr">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>DE26063B</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>298.04</v>
+      </c>
+      <c r="F96" s="4">
+        <f>D96*E96</f>
+        <v/>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="H96" s="4">
+        <f>F96-G96</f>
+        <v/>
+      </c>
+      <c r="I96" s="5">
+        <f>IF(F96&gt;0, H96/F96, 0)</f>
+        <v/>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr"/>
-      <c r="C96" s="6" t="inlineStr"/>
-      <c r="D96" s="7">
-        <f>SUM(D2:D95)</f>
-        <v/>
-      </c>
-      <c r="E96" s="6" t="inlineStr"/>
-      <c r="F96" s="8">
-        <f>SUM(F2:F95)</f>
-        <v/>
-      </c>
-      <c r="G96" s="8">
-        <f>SUM(G2:G95)</f>
-        <v/>
-      </c>
-      <c r="H96" s="8">
-        <f>SUM(H2:H95)</f>
-        <v/>
-      </c>
-      <c r="I96" s="9">
-        <f>IF(F96&gt;0, H96/F96, 0)</f>
-        <v/>
-      </c>
-      <c r="J96" s="6" t="inlineStr"/>
+      <c r="B97" s="6" t="inlineStr"/>
+      <c r="C97" s="6" t="inlineStr"/>
+      <c r="D97" s="7">
+        <f>SUM(D2:D96)</f>
+        <v/>
+      </c>
+      <c r="E97" s="6" t="inlineStr"/>
+      <c r="F97" s="8">
+        <f>SUM(F2:F96)</f>
+        <v/>
+      </c>
+      <c r="G97" s="8">
+        <f>SUM(G2:G96)</f>
+        <v/>
+      </c>
+      <c r="H97" s="8">
+        <f>SUM(H2:H96)</f>
+        <v/>
+      </c>
+      <c r="I97" s="9">
+        <f>IF(F97&gt;0, H97/F97, 0)</f>
+        <v/>
+      </c>
+      <c r="J97" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4449,7 +4490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5575,7 +5616,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
@@ -5605,11 +5646,11 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>DE26016B</t>
+          <t>DE26011N</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>0</v>
@@ -5628,7 +5669,7 @@
         <v/>
       </c>
       <c r="H29" s="4" t="n">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="I29" s="4">
         <f>G29*H29</f>
@@ -5645,14 +5686,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>DE26016R</t>
+          <t>DE26016B</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>0</v>
@@ -5675,7 +5716,7 @@
         <v/>
       </c>
       <c r="J30" s="4" t="n">
-        <v>57.51</v>
+        <v>0</v>
       </c>
       <c r="K30" s="2">
         <f>IF(G30&gt;10, "In Stock", IF(G30&gt;0, "Low Stock", IF(G30=0, "Out of Stock", "Over Sold")))</f>
@@ -5685,14 +5726,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>DE26030B</t>
+          <t>DE26016R</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
@@ -5708,14 +5749,14 @@
         <v/>
       </c>
       <c r="H31" s="4" t="n">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="I31" s="4">
         <f>G31*H31</f>
         <v/>
       </c>
       <c r="J31" s="4" t="n">
-        <v>349.52</v>
+        <v>57.51</v>
       </c>
       <c r="K31" s="2">
         <f>IF(G31&gt;10, "In Stock", IF(G31&gt;0, "Low Stock", IF(G31=0, "Out of Stock", "Over Sold")))</f>
@@ -5725,14 +5766,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DE26030M</t>
+          <t>DE26030B</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>0</v>
@@ -5755,7 +5796,7 @@
         <v/>
       </c>
       <c r="J32" s="4" t="n">
-        <v>169.29</v>
+        <v>349.52</v>
       </c>
       <c r="K32" s="2">
         <f>IF(G32&gt;10, "In Stock", IF(G32&gt;0, "Low Stock", IF(G32=0, "Out of Stock", "Over Sold")))</f>
@@ -5765,14 +5806,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>DE26030R</t>
+          <t>DE26030M</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>0</v>
@@ -5795,7 +5836,7 @@
         <v/>
       </c>
       <c r="J33" s="4" t="n">
-        <v>351.95</v>
+        <v>169.29</v>
       </c>
       <c r="K33" s="2">
         <f>IF(G33&gt;10, "In Stock", IF(G33&gt;0, "Low Stock", IF(G33=0, "Out of Stock", "Over Sold")))</f>
@@ -5805,14 +5846,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>DE26050B</t>
+          <t>DE26030R</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -5828,14 +5869,14 @@
         <v/>
       </c>
       <c r="H34" s="4" t="n">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="I34" s="4">
         <f>G34*H34</f>
         <v/>
       </c>
       <c r="J34" s="4" t="n">
-        <v>204.92</v>
+        <v>351.95</v>
       </c>
       <c r="K34" s="2">
         <f>IF(G34&gt;10, "In Stock", IF(G34&gt;0, "Low Stock", IF(G34=0, "Out of Stock", "Over Sold")))</f>
@@ -5845,14 +5886,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>DE26063B</t>
+          <t>DE26050B</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>0</v>
@@ -5868,14 +5909,14 @@
         <v/>
       </c>
       <c r="H35" s="4" t="n">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="I35" s="4">
         <f>G35*H35</f>
         <v/>
       </c>
       <c r="J35" s="4" t="n">
-        <v>62.93</v>
+        <v>204.92</v>
       </c>
       <c r="K35" s="2">
         <f>IF(G35&gt;10, "In Stock", IF(G35&gt;0, "Low Stock", IF(G35=0, "Out of Stock", "Over Sold")))</f>
@@ -5885,14 +5926,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>DE26063W</t>
+          <t>DE26063B</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
@@ -5915,7 +5956,7 @@
         <v/>
       </c>
       <c r="J36" s="4" t="n">
-        <v>76.65000000000001</v>
+        <v>141.97</v>
       </c>
       <c r="K36" s="2">
         <f>IF(G36&gt;10, "In Stock", IF(G36&gt;0, "Low Stock", IF(G36=0, "Out of Stock", "Over Sold")))</f>
@@ -5925,14 +5966,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>DE26077N</t>
+          <t>DE26063W</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
@@ -5948,14 +5989,14 @@
         <v/>
       </c>
       <c r="H37" s="4" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I37" s="4">
         <f>G37*H37</f>
         <v/>
       </c>
       <c r="J37" s="4" t="n">
-        <v>465.25</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="K37" s="2">
         <f>IF(G37&gt;10, "In Stock", IF(G37&gt;0, "Low Stock", IF(G37=0, "Out of Stock", "Over Sold")))</f>
@@ -5965,20 +6006,20 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>DE26077R</t>
+          <t>DE26077N</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>0</v>
@@ -5995,7 +6036,7 @@
         <v/>
       </c>
       <c r="J38" s="4" t="n">
-        <v>905.17</v>
+        <v>465.25</v>
       </c>
       <c r="K38" s="2">
         <f>IF(G38&gt;10, "In Stock", IF(G38&gt;0, "Low Stock", IF(G38=0, "Out of Stock", "Over Sold")))</f>
@@ -6005,14 +6046,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>DE26077Y</t>
+          <t>DE26077R</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
         <v>12</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>0</v>
@@ -6035,7 +6076,7 @@
         <v/>
       </c>
       <c r="J39" s="4" t="n">
-        <v>607.84</v>
+        <v>905.17</v>
       </c>
       <c r="K39" s="2">
         <f>IF(G39&gt;10, "In Stock", IF(G39&gt;0, "Low Stock", IF(G39=0, "Out of Stock", "Over Sold")))</f>
@@ -6045,20 +6086,20 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>DE26081M</t>
+          <t>DE26077Y</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>0</v>
@@ -6068,14 +6109,14 @@
         <v/>
       </c>
       <c r="H40" s="4" t="n">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="I40" s="4">
         <f>G40*H40</f>
         <v/>
       </c>
       <c r="J40" s="4" t="n">
-        <v>80.67</v>
+        <v>607.84</v>
       </c>
       <c r="K40" s="2">
         <f>IF(G40&gt;10, "In Stock", IF(G40&gt;0, "Low Stock", IF(G40=0, "Out of Stock", "Over Sold")))</f>
@@ -6085,14 +6126,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>DE26081N</t>
+          <t>DE26081M</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>0</v>
@@ -6115,7 +6156,7 @@
         <v/>
       </c>
       <c r="J41" s="4" t="n">
-        <v>0</v>
+        <v>80.67</v>
       </c>
       <c r="K41" s="2">
         <f>IF(G41&gt;10, "In Stock", IF(G41&gt;0, "Low Stock", IF(G41=0, "Out of Stock", "Over Sold")))</f>
@@ -6125,7 +6166,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>DE26081R</t>
+          <t>DE26081N</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
@@ -6163,45 +6204,85 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>DE26081R</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <f>B43-C43+F43</f>
+        <v/>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="I43" s="4">
+        <f>G43*H43</f>
+        <v/>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="2">
+        <f>IF(G43&gt;10, "In Stock", IF(G43&gt;0, "Low Stock", IF(G43=0, "Out of Stock", "Over Sold")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B43" s="7">
-        <f>SUM(B2:B42)</f>
-        <v/>
-      </c>
-      <c r="C43" s="7">
-        <f>SUM(C2:C42)</f>
-        <v/>
-      </c>
-      <c r="D43" s="7">
-        <f>SUM(D2:D42)</f>
-        <v/>
-      </c>
-      <c r="E43" s="7">
-        <f>SUM(E2:E42)</f>
-        <v/>
-      </c>
-      <c r="F43" s="7">
-        <f>SUM(F2:F42)</f>
-        <v/>
-      </c>
-      <c r="G43" s="7">
-        <f>SUM(G2:G42)</f>
-        <v/>
-      </c>
-      <c r="H43" s="6" t="inlineStr"/>
-      <c r="I43" s="8">
-        <f>SUM(I2:I42)</f>
-        <v/>
-      </c>
-      <c r="J43" s="8">
-        <f>SUM(J2:J42)</f>
-        <v/>
-      </c>
-      <c r="K43" s="6" t="inlineStr"/>
+      <c r="B44" s="7">
+        <f>SUM(B2:B43)</f>
+        <v/>
+      </c>
+      <c r="C44" s="7">
+        <f>SUM(C2:C43)</f>
+        <v/>
+      </c>
+      <c r="D44" s="7">
+        <f>SUM(D2:D43)</f>
+        <v/>
+      </c>
+      <c r="E44" s="7">
+        <f>SUM(E2:E43)</f>
+        <v/>
+      </c>
+      <c r="F44" s="7">
+        <f>SUM(F2:F43)</f>
+        <v/>
+      </c>
+      <c r="G44" s="7">
+        <f>SUM(G2:G43)</f>
+        <v/>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="8">
+        <f>SUM(I2:I43)</f>
+        <v/>
+      </c>
+      <c r="J44" s="8">
+        <f>SUM(J2:J43)</f>
+        <v/>
+      </c>
+      <c r="K44" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6214,7 +6295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6850,31 +6931,74 @@
       <c r="L13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>RTO-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>DE26009Y</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>294.62</v>
+      </c>
+      <c r="F14" s="4">
+        <f>D14*E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>In Transit</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Delhivery AWB-1490841473188476</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="7">
-        <f>SUM(D2:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="8">
-        <f>SUM(F2:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="8">
-        <f>SUM(G2:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
-      <c r="L14" s="6" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="7">
+        <f>SUM(D2:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="8">
+        <f>SUM(F2:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="8">
+        <f>SUM(G2:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6896,7 +7020,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="61" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -7264,7 +7388,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Have other quality related issues</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -7274,10 +7398,14 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>In Transit</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -7323,10 +7451,14 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>In Transit</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -7362,7 +7494,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Received wrong product (different color / size / product)</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -8221,7 +8353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -8595,18 +8727,39 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Credited (+)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>3921.55</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>-105711.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr"/>
-      <c r="C18" s="6" t="inlineStr"/>
-      <c r="D18" s="8">
-        <f>SUM(D2:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="6" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="8">
+        <f>SUM(D2:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8619,7 +8772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -9506,33 +9659,60 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>298.04</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="F33" s="4">
+        <f>D33-E33</f>
+        <v/>
+      </c>
+      <c r="G33" s="5">
+        <f>IF(D33&gt;0, F33/D33, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>SUM(B2:B32)</f>
-        <v/>
-      </c>
-      <c r="C33" s="7">
-        <f>SUM(C2:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="8">
-        <f>SUM(D2:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="8">
-        <f>SUM(E2:E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="8">
-        <f>SUM(F2:F32)</f>
-        <v/>
-      </c>
-      <c r="G33" s="9">
-        <f>IF(D33&gt;0, F33/D33, 0)</f>
+      <c r="B34" s="7">
+        <f>SUM(B2:B33)</f>
+        <v/>
+      </c>
+      <c r="C34" s="7">
+        <f>SUM(C2:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="8">
+        <f>SUM(D2:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="8">
+        <f>SUM(E2:E33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="8">
+        <f>SUM(F2:F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="9">
+        <f>IF(D34&gt;0, F34/D34, 0)</f>
         <v/>
       </c>
     </row>

--- a/Sales_Inventory.xlsx
+++ b/Sales_Inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -496,8 +496,8 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="29" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4449,35 +4449,1634 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="6" t="inlineStr">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>DE26009G</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>305.85</v>
+      </c>
+      <c r="F97" s="4">
+        <f>D97*E97</f>
+        <v/>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="H97" s="4">
+        <f>F97-G97</f>
+        <v/>
+      </c>
+      <c r="I97" s="5">
+        <f>IF(F97&gt;0, H97/F97, 0)</f>
+        <v/>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>DE26002N</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>339.29</v>
+      </c>
+      <c r="F98" s="4">
+        <f>D98*E98</f>
+        <v/>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H98" s="4">
+        <f>F98-G98</f>
+        <v/>
+      </c>
+      <c r="I98" s="5">
+        <f>IF(F98&gt;0, H98/F98, 0)</f>
+        <v/>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>DE26005N</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>302.77</v>
+      </c>
+      <c r="F99" s="4">
+        <f>D99*E99</f>
+        <v/>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H99" s="4">
+        <f>F99-G99</f>
+        <v/>
+      </c>
+      <c r="I99" s="5">
+        <f>IF(F99&gt;0, H99/F99, 0)</f>
+        <v/>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>DE26007N</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>293.21</v>
+      </c>
+      <c r="F100" s="4">
+        <f>D100*E100</f>
+        <v/>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H100" s="4">
+        <f>F100-G100</f>
+        <v/>
+      </c>
+      <c r="I100" s="5">
+        <f>IF(F100&gt;0, H100/F100, 0)</f>
+        <v/>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>DE26003W</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>311.54</v>
+      </c>
+      <c r="F101" s="4">
+        <f>D101*E101</f>
+        <v/>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="H101" s="4">
+        <f>F101-G101</f>
+        <v/>
+      </c>
+      <c r="I101" s="5">
+        <f>IF(F101&gt;0, H101/F101, 0)</f>
+        <v/>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>DE26003B</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>313.35</v>
+      </c>
+      <c r="F102" s="4">
+        <f>D102*E102</f>
+        <v/>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="H102" s="4">
+        <f>F102-G102</f>
+        <v/>
+      </c>
+      <c r="I102" s="5">
+        <f>IF(F102&gt;0, H102/F102, 0)</f>
+        <v/>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>DE26007N</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>336.7</v>
+      </c>
+      <c r="F103" s="4">
+        <f>D103*E103</f>
+        <v/>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H103" s="4">
+        <f>F103-G103</f>
+        <v/>
+      </c>
+      <c r="I103" s="5">
+        <f>IF(F103&gt;0, H103/F103, 0)</f>
+        <v/>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>DE26077Y</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>296.79</v>
+      </c>
+      <c r="F104" s="4">
+        <f>D104*E104</f>
+        <v/>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="H104" s="4">
+        <f>F104-G104</f>
+        <v/>
+      </c>
+      <c r="I104" s="5">
+        <f>IF(F104&gt;0, H104/F104, 0)</f>
+        <v/>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>DE26009G</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>328.33</v>
+      </c>
+      <c r="F105" s="4">
+        <f>D105*E105</f>
+        <v/>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="H105" s="4">
+        <f>F105-G105</f>
+        <v/>
+      </c>
+      <c r="I105" s="5">
+        <f>IF(F105&gt;0, H105/F105, 0)</f>
+        <v/>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>DE26007N</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>312.86</v>
+      </c>
+      <c r="F106" s="4">
+        <f>D106*E106</f>
+        <v/>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H106" s="4">
+        <f>F106-G106</f>
+        <v/>
+      </c>
+      <c r="I106" s="5">
+        <f>IF(F106&gt;0, H106/F106, 0)</f>
+        <v/>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>DE26003W</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>311.73</v>
+      </c>
+      <c r="F107" s="4">
+        <f>D107*E107</f>
+        <v/>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="H107" s="4">
+        <f>F107-G107</f>
+        <v/>
+      </c>
+      <c r="I107" s="5">
+        <f>IF(F107&gt;0, H107/F107, 0)</f>
+        <v/>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>DE26010G</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>251.77</v>
+      </c>
+      <c r="F108" s="4">
+        <f>D108*E108</f>
+        <v/>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H108" s="4">
+        <f>F108-G108</f>
+        <v/>
+      </c>
+      <c r="I108" s="5">
+        <f>IF(F108&gt;0, H108/F108, 0)</f>
+        <v/>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>DE26010N</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>276.44</v>
+      </c>
+      <c r="F109" s="4">
+        <f>D109*E109</f>
+        <v/>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H109" s="4">
+        <f>F109-G109</f>
+        <v/>
+      </c>
+      <c r="I109" s="5">
+        <f>IF(F109&gt;0, H109/F109, 0)</f>
+        <v/>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>DE26011P</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>275.64</v>
+      </c>
+      <c r="F110" s="4">
+        <f>D110*E110</f>
+        <v/>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H110" s="4">
+        <f>F110-G110</f>
+        <v/>
+      </c>
+      <c r="I110" s="5">
+        <f>IF(F110&gt;0, H110/F110, 0)</f>
+        <v/>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>DE26081N</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>293.09</v>
+      </c>
+      <c r="F111" s="4">
+        <f>D111*E111</f>
+        <v/>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H111" s="4">
+        <f>F111-G111</f>
+        <v/>
+      </c>
+      <c r="I111" s="5">
+        <f>IF(F111&gt;0, H111/F111, 0)</f>
+        <v/>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>DE26009B</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="4" t="n">
+        <v>328.52</v>
+      </c>
+      <c r="F112" s="4">
+        <f>D112*E112</f>
+        <v/>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="H112" s="4">
+        <f>F112-G112</f>
+        <v/>
+      </c>
+      <c r="I112" s="5">
+        <f>IF(F112&gt;0, H112/F112, 0)</f>
+        <v/>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>DE26010M</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="F113" s="4">
+        <f>D113*E113</f>
+        <v/>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H113" s="4">
+        <f>F113-G113</f>
+        <v/>
+      </c>
+      <c r="I113" s="5">
+        <f>IF(F113&gt;0, H113/F113, 0)</f>
+        <v/>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>DE26010R</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>274.66</v>
+      </c>
+      <c r="F114" s="4">
+        <f>D114*E114</f>
+        <v/>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H114" s="4">
+        <f>F114-G114</f>
+        <v/>
+      </c>
+      <c r="I114" s="5">
+        <f>IF(F114&gt;0, H114/F114, 0)</f>
+        <v/>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>DE26011R</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>253.57</v>
+      </c>
+      <c r="F115" s="4">
+        <f>D115*E115</f>
+        <v/>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H115" s="4">
+        <f>F115-G115</f>
+        <v/>
+      </c>
+      <c r="I115" s="5">
+        <f>IF(F115&gt;0, H115/F115, 0)</f>
+        <v/>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>DE26011B</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>253.51</v>
+      </c>
+      <c r="F116" s="4">
+        <f>D116*E116</f>
+        <v/>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H116" s="4">
+        <f>F116-G116</f>
+        <v/>
+      </c>
+      <c r="I116" s="5">
+        <f>IF(F116&gt;0, H116/F116, 0)</f>
+        <v/>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>DE26030R</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>316.58</v>
+      </c>
+      <c r="F117" s="4">
+        <f>D117*E117</f>
+        <v/>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="H117" s="4">
+        <f>F117-G117</f>
+        <v/>
+      </c>
+      <c r="I117" s="5">
+        <f>IF(F117&gt;0, H117/F117, 0)</f>
+        <v/>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>DE26030R</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>336.66</v>
+      </c>
+      <c r="F118" s="4">
+        <f>D118*E118</f>
+        <v/>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="H118" s="4">
+        <f>F118-G118</f>
+        <v/>
+      </c>
+      <c r="I118" s="5">
+        <f>IF(F118&gt;0, H118/F118, 0)</f>
+        <v/>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>DE26010B</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="F119" s="4">
+        <f>D119*E119</f>
+        <v/>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H119" s="4">
+        <f>F119-G119</f>
+        <v/>
+      </c>
+      <c r="I119" s="5">
+        <f>IF(F119&gt;0, H119/F119, 0)</f>
+        <v/>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>DE26010G</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>276.25</v>
+      </c>
+      <c r="F120" s="4">
+        <f>D120*E120</f>
+        <v/>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>555</v>
+      </c>
+      <c r="H120" s="4">
+        <f>F120-G120</f>
+        <v/>
+      </c>
+      <c r="I120" s="5">
+        <f>IF(F120&gt;0, H120/F120, 0)</f>
+        <v/>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>DE26011R</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>276.44</v>
+      </c>
+      <c r="F121" s="4">
+        <f>D121*E121</f>
+        <v/>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H121" s="4">
+        <f>F121-G121</f>
+        <v/>
+      </c>
+      <c r="I121" s="5">
+        <f>IF(F121&gt;0, H121/F121, 0)</f>
+        <v/>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>DE26010R</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>276.32</v>
+      </c>
+      <c r="F122" s="4">
+        <f>D122*E122</f>
+        <v/>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H122" s="4">
+        <f>F122-G122</f>
+        <v/>
+      </c>
+      <c r="I122" s="5">
+        <f>IF(F122&gt;0, H122/F122, 0)</f>
+        <v/>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>DE26077Y</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>315.63</v>
+      </c>
+      <c r="F123" s="4">
+        <f>D123*E123</f>
+        <v/>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="H123" s="4">
+        <f>F123-G123</f>
+        <v/>
+      </c>
+      <c r="I123" s="5">
+        <f>IF(F123&gt;0, H123/F123, 0)</f>
+        <v/>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>DE26011B</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>253.57</v>
+      </c>
+      <c r="F124" s="4">
+        <f>D124*E124</f>
+        <v/>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H124" s="4">
+        <f>F124-G124</f>
+        <v/>
+      </c>
+      <c r="I124" s="5">
+        <f>IF(F124&gt;0, H124/F124, 0)</f>
+        <v/>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>DE26010G</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>275.98</v>
+      </c>
+      <c r="F125" s="4">
+        <f>D125*E125</f>
+        <v/>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="H125" s="4">
+        <f>F125-G125</f>
+        <v/>
+      </c>
+      <c r="I125" s="5">
+        <f>IF(F125&gt;0, H125/F125, 0)</f>
+        <v/>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>DE26011P</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>254.66</v>
+      </c>
+      <c r="F126" s="4">
+        <f>D126*E126</f>
+        <v/>
+      </c>
+      <c r="G126" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H126" s="4">
+        <f>F126-G126</f>
+        <v/>
+      </c>
+      <c r="I126" s="5">
+        <f>IF(F126&gt;0, H126/F126, 0)</f>
+        <v/>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>DE26010M</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="4" t="n">
+        <v>275.69</v>
+      </c>
+      <c r="F127" s="4">
+        <f>D127*E127</f>
+        <v/>
+      </c>
+      <c r="G127" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H127" s="4">
+        <f>F127-G127</f>
+        <v/>
+      </c>
+      <c r="I127" s="5">
+        <f>IF(F127&gt;0, H127/F127, 0)</f>
+        <v/>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>DE26010N</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="F128" s="4">
+        <f>D128*E128</f>
+        <v/>
+      </c>
+      <c r="G128" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H128" s="4">
+        <f>F128-G128</f>
+        <v/>
+      </c>
+      <c r="I128" s="5">
+        <f>IF(F128&gt;0, H128/F128, 0)</f>
+        <v/>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>DE26081R</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>336.61</v>
+      </c>
+      <c r="F129" s="4">
+        <f>D129*E129</f>
+        <v/>
+      </c>
+      <c r="G129" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="H129" s="4">
+        <f>F129-G129</f>
+        <v/>
+      </c>
+      <c r="I129" s="5">
+        <f>IF(F129&gt;0, H129/F129, 0)</f>
+        <v/>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>DE26010G</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>275.57</v>
+      </c>
+      <c r="F130" s="4">
+        <f>D130*E130</f>
+        <v/>
+      </c>
+      <c r="G130" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H130" s="4">
+        <f>F130-G130</f>
+        <v/>
+      </c>
+      <c r="I130" s="5">
+        <f>IF(F130&gt;0, H130/F130, 0)</f>
+        <v/>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>DE26010N</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="4" t="n">
+        <v>254.68</v>
+      </c>
+      <c r="F131" s="4">
+        <f>D131*E131</f>
+        <v/>
+      </c>
+      <c r="G131" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H131" s="4">
+        <f>F131-G131</f>
+        <v/>
+      </c>
+      <c r="I131" s="5">
+        <f>IF(F131&gt;0, H131/F131, 0)</f>
+        <v/>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>DE26010R</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>276.33</v>
+      </c>
+      <c r="F132" s="4">
+        <f>D132*E132</f>
+        <v/>
+      </c>
+      <c r="G132" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H132" s="4">
+        <f>F132-G132</f>
+        <v/>
+      </c>
+      <c r="I132" s="5">
+        <f>IF(F132&gt;0, H132/F132, 0)</f>
+        <v/>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>DE26011G</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>275.57</v>
+      </c>
+      <c r="F133" s="4">
+        <f>D133*E133</f>
+        <v/>
+      </c>
+      <c r="G133" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="H133" s="4">
+        <f>F133-G133</f>
+        <v/>
+      </c>
+      <c r="I133" s="5">
+        <f>IF(F133&gt;0, H133/F133, 0)</f>
+        <v/>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>DE26012B</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" s="4" t="n">
+        <v>312.37</v>
+      </c>
+      <c r="F134" s="4">
+        <f>D134*E134</f>
+        <v/>
+      </c>
+      <c r="G134" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="H134" s="4">
+        <f>F134-G134</f>
+        <v/>
+      </c>
+      <c r="I134" s="5">
+        <f>IF(F134&gt;0, H134/F134, 0)</f>
+        <v/>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>DE26077Y</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" s="4" t="n">
+        <v>317.2</v>
+      </c>
+      <c r="F135" s="4">
+        <f>D135*E135</f>
+        <v/>
+      </c>
+      <c r="G135" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="H135" s="4">
+        <f>F135-G135</f>
+        <v/>
+      </c>
+      <c r="I135" s="5">
+        <f>IF(F135&gt;0, H135/F135, 0)</f>
+        <v/>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr"/>
-      <c r="C97" s="6" t="inlineStr"/>
-      <c r="D97" s="7">
-        <f>SUM(D2:D96)</f>
-        <v/>
-      </c>
-      <c r="E97" s="6" t="inlineStr"/>
-      <c r="F97" s="8">
-        <f>SUM(F2:F96)</f>
-        <v/>
-      </c>
-      <c r="G97" s="8">
-        <f>SUM(G2:G96)</f>
-        <v/>
-      </c>
-      <c r="H97" s="8">
-        <f>SUM(H2:H96)</f>
-        <v/>
-      </c>
-      <c r="I97" s="9">
-        <f>IF(F97&gt;0, H97/F97, 0)</f>
-        <v/>
-      </c>
-      <c r="J97" s="6" t="inlineStr"/>
+      <c r="B136" s="6" t="inlineStr"/>
+      <c r="C136" s="6" t="inlineStr"/>
+      <c r="D136" s="7">
+        <f>SUM(D2:D135)</f>
+        <v/>
+      </c>
+      <c r="E136" s="6" t="inlineStr"/>
+      <c r="F136" s="8">
+        <f>SUM(F2:F135)</f>
+        <v/>
+      </c>
+      <c r="G136" s="8">
+        <f>SUM(G2:G135)</f>
+        <v/>
+      </c>
+      <c r="H136" s="8">
+        <f>SUM(H2:H135)</f>
+        <v/>
+      </c>
+      <c r="I136" s="9">
+        <f>IF(F136&gt;0, H136/F136, 0)</f>
+        <v/>
+      </c>
+      <c r="J136" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4490,7 +6089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4773,7 +6372,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -4796,7 +6395,7 @@
         <v/>
       </c>
       <c r="J7" s="4" t="n">
-        <v>341.42</v>
+        <v>445.71</v>
       </c>
       <c r="K7" s="2">
         <f>IF(G7&gt;10, "In Stock", IF(G7&gt;0, "Low Stock", IF(G7=0, "Out of Stock", "Over Sold")))</f>
@@ -4816,7 +6415,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>1</v>
@@ -4853,7 +6452,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -4876,7 +6475,7 @@
         <v/>
       </c>
       <c r="J9" s="4" t="n">
-        <v>912.39</v>
+        <v>1006.74</v>
       </c>
       <c r="K9" s="2">
         <f>IF(G9&gt;10, "In Stock", IF(G9&gt;0, "Low Stock", IF(G9=0, "Out of Stock", "Over Sold")))</f>
@@ -4893,7 +6492,7 @@
         <v>30</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -4916,7 +6515,7 @@
         <v/>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2399.64</v>
+        <v>2584.91</v>
       </c>
       <c r="K10" s="2">
         <f>IF(G10&gt;10, "In Stock", IF(G10&gt;0, "Low Stock", IF(G10=0, "Out of Stock", "Over Sold")))</f>
@@ -5093,7 +6692,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -5116,7 +6715,7 @@
         <v/>
       </c>
       <c r="J15" s="4" t="n">
-        <v>105.34</v>
+        <v>173.11</v>
       </c>
       <c r="K15" s="2">
         <f>IF(G15&gt;10, "In Stock", IF(G15&gt;0, "Low Stock", IF(G15=0, "Out of Stock", "Over Sold")))</f>
@@ -5293,7 +6892,7 @@
         <v>7</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
@@ -5316,7 +6915,7 @@
         <v/>
       </c>
       <c r="J20" s="4" t="n">
-        <v>249.26</v>
+        <v>487.03</v>
       </c>
       <c r="K20" s="2">
         <f>IF(G20&gt;10, "In Stock", IF(G20&gt;0, "Low Stock", IF(G20=0, "Out of Stock", "Over Sold")))</f>
@@ -5493,7 +7092,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>0</v>
@@ -5516,7 +7115,7 @@
         <v/>
       </c>
       <c r="J25" s="4" t="n">
-        <v>183.09</v>
+        <v>286.61</v>
       </c>
       <c r="K25" s="2">
         <f>IF(G25&gt;10, "In Stock", IF(G25&gt;0, "Low Stock", IF(G25=0, "Out of Stock", "Over Sold")))</f>
@@ -5533,10 +7132,10 @@
         <v>12</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>0</v>
@@ -5556,7 +7155,7 @@
         <v/>
       </c>
       <c r="J26" s="4" t="n">
-        <v>516.08</v>
+        <v>803.59</v>
       </c>
       <c r="K26" s="2">
         <f>IF(G26&gt;10, "In Stock", IF(G26&gt;0, "Low Stock", IF(G26=0, "Out of Stock", "Over Sold")))</f>
@@ -5576,10 +7175,10 @@
         <v>1</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0</v>
@@ -5616,10 +7215,10 @@
         <v>1</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -5646,14 +7245,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>DE26011N</t>
+          <t>DE26010B</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
@@ -5676,7 +7275,7 @@
         <v/>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="K29" s="2">
         <f>IF(G29&gt;10, "In Stock", IF(G29&gt;0, "Low Stock", IF(G29=0, "Out of Stock", "Over Sold")))</f>
@@ -5686,14 +7285,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>DE26016B</t>
+          <t>DE26010G</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>0</v>
@@ -5709,14 +7308,14 @@
         <v/>
       </c>
       <c r="H30" s="4" t="n">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="I30" s="4">
         <f>G30*H30</f>
         <v/>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0</v>
+        <v>613.05</v>
       </c>
       <c r="K30" s="2">
         <f>IF(G30&gt;10, "In Stock", IF(G30&gt;0, "Low Stock", IF(G30=0, "Out of Stock", "Over Sold")))</f>
@@ -5726,14 +7325,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>DE26016R</t>
+          <t>DE26010M</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
@@ -5749,14 +7348,14 @@
         <v/>
       </c>
       <c r="H31" s="4" t="n">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="I31" s="4">
         <f>G31*H31</f>
         <v/>
       </c>
       <c r="J31" s="4" t="n">
-        <v>57.51</v>
+        <v>182.39</v>
       </c>
       <c r="K31" s="2">
         <f>IF(G31&gt;10, "In Stock", IF(G31&gt;0, "Low Stock", IF(G31=0, "Out of Stock", "Over Sold")))</f>
@@ -5766,14 +7365,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DE26030B</t>
+          <t>DE26010N</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>0</v>
@@ -5789,14 +7388,14 @@
         <v/>
       </c>
       <c r="H32" s="4" t="n">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="I32" s="4">
         <f>G32*H32</f>
         <v/>
       </c>
       <c r="J32" s="4" t="n">
-        <v>349.52</v>
+        <v>252.82</v>
       </c>
       <c r="K32" s="2">
         <f>IF(G32&gt;10, "In Stock", IF(G32&gt;0, "Low Stock", IF(G32=0, "Out of Stock", "Over Sold")))</f>
@@ -5806,14 +7405,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>DE26030M</t>
+          <t>DE26010R</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>0</v>
@@ -5829,14 +7428,14 @@
         <v/>
       </c>
       <c r="H33" s="4" t="n">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="I33" s="4">
         <f>G33*H33</f>
         <v/>
       </c>
       <c r="J33" s="4" t="n">
-        <v>169.29</v>
+        <v>272.31</v>
       </c>
       <c r="K33" s="2">
         <f>IF(G33&gt;10, "In Stock", IF(G33&gt;0, "Low Stock", IF(G33=0, "Out of Stock", "Over Sold")))</f>
@@ -5846,14 +7445,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>DE26030R</t>
+          <t>DE26011B</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -5869,14 +7468,14 @@
         <v/>
       </c>
       <c r="H34" s="4" t="n">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="I34" s="4">
         <f>G34*H34</f>
         <v/>
       </c>
       <c r="J34" s="4" t="n">
-        <v>351.95</v>
+        <v>137.08</v>
       </c>
       <c r="K34" s="2">
         <f>IF(G34&gt;10, "In Stock", IF(G34&gt;0, "Low Stock", IF(G34=0, "Out of Stock", "Over Sold")))</f>
@@ -5886,14 +7485,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>DE26050B</t>
+          <t>DE26011G</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>0</v>
@@ -5909,14 +7508,14 @@
         <v/>
       </c>
       <c r="H35" s="4" t="n">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="I35" s="4">
         <f>G35*H35</f>
         <v/>
       </c>
       <c r="J35" s="4" t="n">
-        <v>204.92</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="K35" s="2">
         <f>IF(G35&gt;10, "In Stock", IF(G35&gt;0, "Low Stock", IF(G35=0, "Out of Stock", "Over Sold")))</f>
@@ -5926,14 +7525,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>DE26063B</t>
+          <t>DE26011N</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
@@ -5949,14 +7548,14 @@
         <v/>
       </c>
       <c r="H36" s="4" t="n">
-        <v>219</v>
+        <v>185</v>
       </c>
       <c r="I36" s="4">
         <f>G36*H36</f>
         <v/>
       </c>
       <c r="J36" s="4" t="n">
-        <v>141.97</v>
+        <v>0</v>
       </c>
       <c r="K36" s="2">
         <f>IF(G36&gt;10, "In Stock", IF(G36&gt;0, "Low Stock", IF(G36=0, "Out of Stock", "Over Sold")))</f>
@@ -5966,14 +7565,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>DE26063W</t>
+          <t>DE26011P</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
@@ -5989,14 +7588,14 @@
         <v/>
       </c>
       <c r="H37" s="4" t="n">
-        <v>219</v>
+        <v>185</v>
       </c>
       <c r="I37" s="4">
         <f>G37*H37</f>
         <v/>
       </c>
       <c r="J37" s="4" t="n">
-        <v>76.65000000000001</v>
+        <v>160.3</v>
       </c>
       <c r="K37" s="2">
         <f>IF(G37&gt;10, "In Stock", IF(G37&gt;0, "Low Stock", IF(G37=0, "Out of Stock", "Over Sold")))</f>
@@ -6006,14 +7605,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>DE26077N</t>
+          <t>DE26011R</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0</v>
@@ -6029,14 +7628,14 @@
         <v/>
       </c>
       <c r="H38" s="4" t="n">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="I38" s="4">
         <f>G38*H38</f>
         <v/>
       </c>
       <c r="J38" s="4" t="n">
-        <v>465.25</v>
+        <v>160.01</v>
       </c>
       <c r="K38" s="2">
         <f>IF(G38&gt;10, "In Stock", IF(G38&gt;0, "Low Stock", IF(G38=0, "Out of Stock", "Over Sold")))</f>
@@ -6046,20 +7645,20 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>DE26077R</t>
+          <t>DE26012B</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
         <v>12</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>0</v>
@@ -6069,14 +7668,14 @@
         <v/>
       </c>
       <c r="H39" s="4" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="I39" s="4">
         <f>G39*H39</f>
         <v/>
       </c>
       <c r="J39" s="4" t="n">
-        <v>905.17</v>
+        <v>87.37</v>
       </c>
       <c r="K39" s="2">
         <f>IF(G39&gt;10, "In Stock", IF(G39&gt;0, "Low Stock", IF(G39=0, "Out of Stock", "Over Sold")))</f>
@@ -6086,20 +7685,20 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>DE26077Y</t>
+          <t>DE26012K</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
         <v>12</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>0</v>
@@ -6109,14 +7708,14 @@
         <v/>
       </c>
       <c r="H40" s="4" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="I40" s="4">
         <f>G40*H40</f>
         <v/>
       </c>
       <c r="J40" s="4" t="n">
-        <v>607.84</v>
+        <v>0</v>
       </c>
       <c r="K40" s="2">
         <f>IF(G40&gt;10, "In Stock", IF(G40&gt;0, "Low Stock", IF(G40=0, "Out of Stock", "Over Sold")))</f>
@@ -6126,14 +7725,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>DE26081M</t>
+          <t>DE26016B</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>0</v>
@@ -6156,7 +7755,7 @@
         <v/>
       </c>
       <c r="J41" s="4" t="n">
-        <v>80.67</v>
+        <v>0</v>
       </c>
       <c r="K41" s="2">
         <f>IF(G41&gt;10, "In Stock", IF(G41&gt;0, "Low Stock", IF(G41=0, "Out of Stock", "Over Sold")))</f>
@@ -6166,14 +7765,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>DE26081N</t>
+          <t>DE26016R</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>0</v>
@@ -6196,7 +7795,7 @@
         <v/>
       </c>
       <c r="J42" s="4" t="n">
-        <v>0</v>
+        <v>57.51</v>
       </c>
       <c r="K42" s="2">
         <f>IF(G42&gt;10, "In Stock", IF(G42&gt;0, "Low Stock", IF(G42=0, "Out of Stock", "Over Sold")))</f>
@@ -6206,14 +7805,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>DE26081R</t>
+          <t>DE26030B</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>0</v>
@@ -6229,14 +7828,14 @@
         <v/>
       </c>
       <c r="H43" s="4" t="n">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="I43" s="4">
         <f>G43*H43</f>
         <v/>
       </c>
       <c r="J43" s="4" t="n">
-        <v>0</v>
+        <v>349.52</v>
       </c>
       <c r="K43" s="2">
         <f>IF(G43&gt;10, "In Stock", IF(G43&gt;0, "Low Stock", IF(G43=0, "Out of Stock", "Over Sold")))</f>
@@ -6244,45 +7843,485 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>DE26030M</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <f>B44-C44+F44</f>
+        <v/>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="I44" s="4">
+        <f>G44*H44</f>
+        <v/>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>169.29</v>
+      </c>
+      <c r="K44" s="2">
+        <f>IF(G44&gt;10, "In Stock", IF(G44&gt;0, "Low Stock", IF(G44=0, "Out of Stock", "Over Sold")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>DE26030R</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
+        <f>B45-C45+F45</f>
+        <v/>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="I45" s="4">
+        <f>G45*H45</f>
+        <v/>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>595.1900000000001</v>
+      </c>
+      <c r="K45" s="2">
+        <f>IF(G45&gt;10, "In Stock", IF(G45&gt;0, "Low Stock", IF(G45=0, "Out of Stock", "Over Sold")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>DE26050B</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3">
+        <f>B46-C46+F46</f>
+        <v/>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="I46" s="4">
+        <f>G46*H46</f>
+        <v/>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>204.92</v>
+      </c>
+      <c r="K46" s="2">
+        <f>IF(G46&gt;10, "In Stock", IF(G46&gt;0, "Low Stock", IF(G46=0, "Out of Stock", "Over Sold")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>DE26063B</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <f>B47-C47+F47</f>
+        <v/>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="I47" s="4">
+        <f>G47*H47</f>
+        <v/>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>141.97</v>
+      </c>
+      <c r="K47" s="2">
+        <f>IF(G47&gt;10, "In Stock", IF(G47&gt;0, "Low Stock", IF(G47=0, "Out of Stock", "Over Sold")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>DE26063W</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
+        <f>B48-C48+F48</f>
+        <v/>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="I48" s="4">
+        <f>G48*H48</f>
+        <v/>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>76.65000000000001</v>
+      </c>
+      <c r="K48" s="2">
+        <f>IF(G48&gt;10, "In Stock", IF(G48&gt;0, "Low Stock", IF(G48=0, "Out of Stock", "Over Sold")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>DE26077N</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <f>B49-C49+F49</f>
+        <v/>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="I49" s="4">
+        <f>G49*H49</f>
+        <v/>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>465.25</v>
+      </c>
+      <c r="K49" s="2">
+        <f>IF(G49&gt;10, "In Stock", IF(G49&gt;0, "Low Stock", IF(G49=0, "Out of Stock", "Over Sold")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>DE26077R</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3">
+        <f>B50-C50+F50</f>
+        <v/>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="I50" s="4">
+        <f>G50*H50</f>
+        <v/>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>905.17</v>
+      </c>
+      <c r="K50" s="2">
+        <f>IF(G50&gt;10, "In Stock", IF(G50&gt;0, "Low Stock", IF(G50=0, "Out of Stock", "Over Sold")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>DE26077Y</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3">
+        <f>B51-C51+F51</f>
+        <v/>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="I51" s="4">
+        <f>G51*H51</f>
+        <v/>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>974.66</v>
+      </c>
+      <c r="K51" s="2">
+        <f>IF(G51&gt;10, "In Stock", IF(G51&gt;0, "Low Stock", IF(G51=0, "Out of Stock", "Over Sold")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>DE26081M</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <f>B52-C52+F52</f>
+        <v/>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="I52" s="4">
+        <f>G52*H52</f>
+        <v/>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>80.67</v>
+      </c>
+      <c r="K52" s="2">
+        <f>IF(G52&gt;10, "In Stock", IF(G52&gt;0, "Low Stock", IF(G52=0, "Out of Stock", "Over Sold")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>DE26081N</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3">
+        <f>B53-C53+F53</f>
+        <v/>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="I53" s="4">
+        <f>G53*H53</f>
+        <v/>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="K53" s="2">
+        <f>IF(G53&gt;10, "In Stock", IF(G53&gt;0, "Low Stock", IF(G53=0, "Out of Stock", "Over Sold")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>DE26081R</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3">
+        <f>B54-C54+F54</f>
+        <v/>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="I54" s="4">
+        <f>G54*H54</f>
+        <v/>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>101.61</v>
+      </c>
+      <c r="K54" s="2">
+        <f>IF(G54&gt;10, "In Stock", IF(G54&gt;0, "Low Stock", IF(G54=0, "Out of Stock", "Over Sold")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B44" s="7">
-        <f>SUM(B2:B43)</f>
-        <v/>
-      </c>
-      <c r="C44" s="7">
-        <f>SUM(C2:C43)</f>
-        <v/>
-      </c>
-      <c r="D44" s="7">
-        <f>SUM(D2:D43)</f>
-        <v/>
-      </c>
-      <c r="E44" s="7">
-        <f>SUM(E2:E43)</f>
-        <v/>
-      </c>
-      <c r="F44" s="7">
-        <f>SUM(F2:F43)</f>
-        <v/>
-      </c>
-      <c r="G44" s="7">
-        <f>SUM(G2:G43)</f>
-        <v/>
-      </c>
-      <c r="H44" s="6" t="inlineStr"/>
-      <c r="I44" s="8">
-        <f>SUM(I2:I43)</f>
-        <v/>
-      </c>
-      <c r="J44" s="8">
-        <f>SUM(J2:J43)</f>
-        <v/>
-      </c>
-      <c r="K44" s="6" t="inlineStr"/>
+      <c r="B55" s="7">
+        <f>SUM(B2:B54)</f>
+        <v/>
+      </c>
+      <c r="C55" s="7">
+        <f>SUM(C2:C54)</f>
+        <v/>
+      </c>
+      <c r="D55" s="7">
+        <f>SUM(D2:D54)</f>
+        <v/>
+      </c>
+      <c r="E55" s="7">
+        <f>SUM(E2:E54)</f>
+        <v/>
+      </c>
+      <c r="F55" s="7">
+        <f>SUM(F2:F54)</f>
+        <v/>
+      </c>
+      <c r="G55" s="7">
+        <f>SUM(G2:G54)</f>
+        <v/>
+      </c>
+      <c r="H55" s="6" t="inlineStr"/>
+      <c r="I55" s="8">
+        <f>SUM(I2:I54)</f>
+        <v/>
+      </c>
+      <c r="J55" s="8">
+        <f>SUM(J2:J54)</f>
+        <v/>
+      </c>
+      <c r="K55" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6295,7 +8334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6871,10 +8910,14 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>In Transit</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -6961,10 +9004,14 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>In Transit</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -6974,31 +9021,250 @@
       <c r="L14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>RTO-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>DE26063B</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>298.04</v>
+      </c>
+      <c r="F15" s="4">
+        <f>D15*E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Valmo AWB-VL0085538534988</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>RTO-016</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>DE26002R</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>366.77</v>
+      </c>
+      <c r="F16" s="4">
+        <f>D16*E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>In Transit</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Valmo AWB-VL0085458803537</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>RTO-016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>DE26009G</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>328.65</v>
+      </c>
+      <c r="F17" s="4">
+        <f>D17*E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>In Transit</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Valmo AWB-VL0085570188165</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>RTO-018</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>DE26002R</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>333.76</v>
+      </c>
+      <c r="F18" s="4">
+        <f>D18*E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>In Transit</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Xpress Bees AWB-134096134094411</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>RTO-017</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>DE26081N</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>293.09</v>
+      </c>
+      <c r="F19" s="4">
+        <f>D19*E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>In Transit</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Valmo AWB-VL0085612555442</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr"/>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="7">
-        <f>SUM(D2:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="8">
-        <f>SUM(F2:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="8">
-        <f>SUM(G2:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
-      <c r="L15" s="6" t="inlineStr"/>
+      <c r="B20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="7">
+        <f>SUM(D2:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="8">
+        <f>SUM(F2:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="8">
+        <f>SUM(G2:G19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+      <c r="K20" s="6" t="inlineStr"/>
+      <c r="L20" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7011,22 +9277,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="61" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="61" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="121" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7062,35 +9330,45 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Claim Amount ($)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Claim Date</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Primary Reason</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Secondary Reason</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Received Date</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Restocked Date</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Reverse AWB</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -7121,33 +9399,37 @@
       <c r="F2" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Don't need the product anymore</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Did not like the product</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Intake</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Shadowfax  AWB-R2456842272FPL</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -7174,33 +9456,37 @@
       <c r="F3" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Have size / fit related issues</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Did not like the fit</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Intake</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Delhivery AWB-1490711614301402</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -7227,33 +9513,37 @@
       <c r="F4" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Have other quality related issues</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Product's quality or performance is not good</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Intake</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Delhivery AWB-1490711700640883</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -7280,33 +9570,37 @@
       <c r="F5" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Have size / fit related issues</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Size correct but too loose</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Intake</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Shadowfax  AWB-R2470043807FPL</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -7333,33 +9627,37 @@
       <c r="F6" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Have size / fit related issues</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Did not like the fit</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Shadowfax  AWB-R2481671535FPL</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -7386,33 +9684,37 @@
       <c r="F7" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Have other quality related issues</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Product's quality or performance is not good</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Valmo AWB-VLR082916892869</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -7439,33 +9741,45 @@
       <c r="F8" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="n">
+        <v>332.58</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Don't need the product anymore</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Found lower price elsewhere</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Claim Settled</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Valmo AWB-VLR082918756063</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Meesho SPF claim approved for Rs 332.58. Received wrong item inside return parcel; original DE26002M permanently lost</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -7492,57 +9806,294 @@
       <c r="F9" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Received wrong product (different color / size / product)</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Wrong size delivered</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Shadowfax AWB-R2567239146FPL</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CR-010</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>DE26077R</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>297.32</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Received wrong product (different color / size / product)</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Completely different product from shown</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Shadowfax AWB-R2575433805FPL</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CR-009</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>DE26077R</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>297.32</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Don't need the product anymore</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Ordered by mistake</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Shadowfax AWB-R2590709094FPL</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CR-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>DE26077Y</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>297.2</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Have other quality related issues</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Product's quality or performance is not good</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Valmo AWB-VLR082964256945</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>CR-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>DE26077N</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>283.69</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Received wrong product (different color / size / product)</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Completely different product from shown</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>In Transit</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>Shadowfax AWB-R2567239146FPL</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Valmo AWB-VLR082966400477</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr"/>
-      <c r="C10" s="6" t="inlineStr"/>
-      <c r="D10" s="7">
-        <f>SUM(D2:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="8">
-        <f>SUM(E2:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="8">
-        <f>SUM(F2:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr"/>
-      <c r="H10" s="6" t="inlineStr"/>
-      <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="6" t="inlineStr"/>
-      <c r="K10" s="6" t="inlineStr"/>
-      <c r="L10" s="6" t="inlineStr"/>
-      <c r="M10" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="7">
+        <f>SUM(D2:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="8">
+        <f>SUM(E2:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="8">
+        <f>SUM(F2:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="8">
+        <f>SUM(G2:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr"/>
+      <c r="M14" s="6" t="inlineStr"/>
+      <c r="N14" s="6" t="inlineStr"/>
+      <c r="O14" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7672,7 +10223,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -7786,7 +10337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -8330,17 +10881,177 @@
       <c r="D33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>122.08</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>118.41</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>118.73</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>118.09</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>120.36</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>120.11</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>119.46</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>120.43</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>118.52</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>118.94</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr"/>
-      <c r="C34" s="8">
-        <f>SUM(C2:C33)</f>
-        <v/>
-      </c>
-      <c r="D34" s="6" t="inlineStr"/>
+      <c r="B44" s="6" t="inlineStr"/>
+      <c r="C44" s="8">
+        <f>SUM(C2:C43)</f>
+        <v/>
+      </c>
+      <c r="D44" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8353,7 +11064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -8748,18 +11459,186 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Credited (+)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>989.75</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>-104721.95</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Credited (+)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>703.75</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-104018.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Credited (+)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>1104.17</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-102914.03</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Debited (-)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-112914.03</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Credited (+)</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>1335.09</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>-111578.94</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Credited (+)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>186.19</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>-111392.75</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Credited (+)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>1149.32</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>-110243.43</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Credited (+)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>783.33</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>-109460.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr"/>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="8">
-        <f>SUM(D2:D18)</f>
-        <v/>
-      </c>
-      <c r="E19" s="6" t="inlineStr"/>
+      <c r="B27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="8">
+        <f>SUM(D2:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8772,7 +11651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -9665,16 +12544,16 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>298.04</v>
+        <v>603.8900000000001</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>219</v>
+        <v>444</v>
       </c>
       <c r="F33" s="4">
         <f>D33-E33</f>
@@ -9686,33 +12565,357 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>935.27</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>705</v>
+      </c>
+      <c r="F34" s="4">
+        <f>D34-E34</f>
+        <v/>
+      </c>
+      <c r="G34" s="5">
+        <f>IF(D34&gt;0, F34/D34, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>624.8900000000001</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>438</v>
+      </c>
+      <c r="F35" s="4">
+        <f>D35-E35</f>
+        <v/>
+      </c>
+      <c r="G35" s="5">
+        <f>IF(D35&gt;0, F35/D35, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>1290.15</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>905</v>
+      </c>
+      <c r="F36" s="4">
+        <f>D36-E36</f>
+        <v/>
+      </c>
+      <c r="G36" s="5">
+        <f>IF(D36&gt;0, F36/D36, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>312.86</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="F37" s="4">
+        <f>D37-E37</f>
+        <v/>
+      </c>
+      <c r="G37" s="5">
+        <f>IF(D37&gt;0, F37/D37, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>563.5</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>404</v>
+      </c>
+      <c r="F38" s="4">
+        <f>D38-E38</f>
+        <v/>
+      </c>
+      <c r="G38" s="5">
+        <f>IF(D38&gt;0, F38/D38, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>276.44</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="F39" s="4">
+        <f>D39-E39</f>
+        <v/>
+      </c>
+      <c r="G39" s="5">
+        <f>IF(D39&gt;0, F39/D39, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>568.73</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="F40" s="4">
+        <f>D40-E40</f>
+        <v/>
+      </c>
+      <c r="G40" s="5">
+        <f>IF(D40&gt;0, F40/D40, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>1133.45</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>780</v>
+      </c>
+      <c r="F41" s="4">
+        <f>D41-E41</f>
+        <v/>
+      </c>
+      <c r="G41" s="5">
+        <f>IF(D41&gt;0, F41/D41, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>906.75</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>595</v>
+      </c>
+      <c r="F42" s="4">
+        <f>D42-E42</f>
+        <v/>
+      </c>
+      <c r="G42" s="5">
+        <f>IF(D42&gt;0, F42/D42, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>1381.89</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>925</v>
+      </c>
+      <c r="F43" s="4">
+        <f>D43-E43</f>
+        <v/>
+      </c>
+      <c r="G43" s="5">
+        <f>IF(D43&gt;0, F43/D43, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>2541.14</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>1750</v>
+      </c>
+      <c r="F44" s="4">
+        <f>D44-E44</f>
+        <v/>
+      </c>
+      <c r="G44" s="5">
+        <f>IF(D44&gt;0, F44/D44, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>2028.92</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F45" s="4">
+        <f>D45-E45</f>
+        <v/>
+      </c>
+      <c r="G45" s="5">
+        <f>IF(D45&gt;0, F45/D45, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>SUM(B2:B33)</f>
-        <v/>
-      </c>
-      <c r="C34" s="7">
-        <f>SUM(C2:C33)</f>
-        <v/>
-      </c>
-      <c r="D34" s="8">
-        <f>SUM(D2:D33)</f>
-        <v/>
-      </c>
-      <c r="E34" s="8">
-        <f>SUM(E2:E33)</f>
-        <v/>
-      </c>
-      <c r="F34" s="8">
-        <f>SUM(F2:F33)</f>
-        <v/>
-      </c>
-      <c r="G34" s="9">
-        <f>IF(D34&gt;0, F34/D34, 0)</f>
+      <c r="B46" s="7">
+        <f>SUM(B2:B45)</f>
+        <v/>
+      </c>
+      <c r="C46" s="7">
+        <f>SUM(C2:C45)</f>
+        <v/>
+      </c>
+      <c r="D46" s="8">
+        <f>SUM(D2:D45)</f>
+        <v/>
+      </c>
+      <c r="E46" s="8">
+        <f>SUM(E2:E45)</f>
+        <v/>
+      </c>
+      <c r="F46" s="8">
+        <f>SUM(F2:F45)</f>
+        <v/>
+      </c>
+      <c r="G46" s="9">
+        <f>IF(D46&gt;0, F46/D46, 0)</f>
         <v/>
       </c>
     </row>
@@ -9727,7 +12930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -10227,18 +13430,162 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>122.08</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>118.41</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>118.73</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>118.09</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>120.36</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>120.11</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>239.89</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Meesho Ads</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>237.46</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B28" s="7">
-        <f>SUM(B2:B27)</f>
-        <v/>
-      </c>
-      <c r="C28" s="6" t="inlineStr"/>
-      <c r="D28" s="8">
-        <f>SUM(D2:D27)</f>
+      <c r="B36" s="7">
+        <f>SUM(B2:B35)</f>
+        <v/>
+      </c>
+      <c r="C36" s="6" t="inlineStr"/>
+      <c r="D36" s="8">
+        <f>SUM(D2:D35)</f>
         <v/>
       </c>
     </row>
